--- a/out/MLP-S4_repeat_3_000008.xlsx
+++ b/out/MLP-S4_repeat_3_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.086681742285026</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.686681742285026</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.686681742285026</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5212238253023744</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5212238253023744</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.686681742285026</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.686681742285026</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.686681742285026</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.686681742285026</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.086681742285026</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.086681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000161282156629255</v>
+        <v>-0.0001400802099283319</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1852822208733912</v>
+        <v>-0.1609252563232461</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.686681742285026</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.686681742285026</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1855801622144</v>
+        <v>-0.1611864152315984</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4913953041836275</v>
+        <v>0.4353711682502186</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7981539431311669</v>
+        <v>0.7103923643335108</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03501181225172942</v>
+        <v>0.03102010432907314</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5212238253023744</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3759940114468096</v>
+        <v>0.3363625806186774</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06139866110619391</v>
+        <v>0.05439882210839907</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.686681742285026</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4637680940921143</v>
+        <v>0.4141296951803143</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07459243390622572</v>
+        <v>0.06608814441179658</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5515482020194041</v>
+        <v>0.4919019858187302</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01973886192667928</v>
+        <v>0.01748841384980207</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5163385875598644</v>
+        <v>0.4607066224258325</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01096632422859805</v>
+        <v>0.009715655634874901</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.086681742285026</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5185132393532288</v>
+        <v>0.4626327737459778</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02304118677646382</v>
+        <v>0.02041393983913546</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.686681742285026</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5536434304907254</v>
+        <v>0.4937572820178666</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009048986415375181</v>
+        <v>0.00801715168745923</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5486807682013823</v>
+        <v>0.4893599112037255</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006442807535277953</v>
+        <v>0.00570798516769411</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5525141388292953</v>
+        <v>0.4927553872779843</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002532898650642417</v>
+        <v>0.002243667825288305</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5511317429156438</v>
+        <v>0.4915302914631194</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001436221311153854</v>
+        <v>0.00127129010228384</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5514684493514547</v>
+        <v>0.4918278935260622</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000543430430728364</v>
+        <v>0.0004811888615022328</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5511191119218359</v>
+        <v>0.4915179608555997</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002526247437593843</v>
+        <v>0.0002228988117871476</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5510793656646519</v>
+        <v>0.4914822237819368</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.9457059439415e-05</v>
+        <v>7.815450531845937e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5510054389294463</v>
+        <v>0.4914162507023255</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.266517359622213e-05</v>
+        <v>1.980325908626812e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5509616995783185</v>
+        <v>0.4913768153925931</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5509566779836994</v>
+        <v>0.4913717960319002</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5509527686073505</v>
+        <v>0.4913677412390646</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5509505176796189</v>
+        <v>0.4913651238356458</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5509449260196106</v>
+        <v>0.4913596065936561</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5509386020256027</v>
+        <v>0.4913532825996482</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5509332342370243</v>
+        <v>0.4913479148110698</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.550933270985516</v>
+        <v>0.4913479515595615</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5509333812309916</v>
+        <v>0.4913480618050371</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5509334547279752</v>
+        <v>0.4913481353020207</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5509336384704343</v>
+        <v>0.4913483190444798</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5509351819070908</v>
+        <v>0.4913498624811363</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5212238253023744</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5509366518467639</v>
+        <v>0.4913513324208094</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5212238253023744</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5509379012954859</v>
+        <v>0.4913525818695314</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5509392609896833</v>
+        <v>0.4913539415637287</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.686681742285026</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.550937056080174</v>
+        <v>0.4913517366542194</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.686681742285026</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5509366518467639</v>
+        <v>0.4913513324208094</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5212238253023744</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5509358066314519</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5509363578588292</v>
+        <v>0.4913510384328747</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5509360271224027</v>
+        <v>0.4913507076964483</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5509357331344683</v>
+        <v>0.4913504137085138</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5509358066314519</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.55093536564955</v>
+        <v>0.4913500462235955</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5509352554040744</v>
+        <v>0.4913499359781199</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5509352186555827</v>
+        <v>0.4913498992296282</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.55093536564955</v>
+        <v>0.4913500462235955</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5509348879191563</v>
+        <v>0.4913495684932019</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.686681742285026</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5509358433799436</v>
+        <v>0.4913505239539891</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5509358066314519</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5509354758950256</v>
+        <v>0.491350156469071</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5509359168769274</v>
+        <v>0.491350597450973</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5509352921525664</v>
+        <v>0.4913499727266119</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5509351084101072</v>
+        <v>0.4913497889841527</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5509347041766972</v>
+        <v>0.4913493847507427</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5509338589613852</v>
+        <v>0.4913485395354307</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5509338222128936</v>
+        <v>0.491348502786939</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5509339692068608</v>
+        <v>0.4913486497809063</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5509338957098772</v>
+        <v>0.4913485762839226</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5509339692068608</v>
+        <v>0.4913486497809063</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5509340059553527</v>
+        <v>0.4913486865293982</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5509338957098772</v>
+        <v>0.4913485762839226</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.550934336691779</v>
+        <v>0.4913490172658246</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5509342264463035</v>
+        <v>0.4913489070203491</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5509341896978116</v>
+        <v>0.4913488702718571</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.550934116200828</v>
+        <v>0.4913487967748735</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5509340794523363</v>
+        <v>0.4913487600263818</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5509338589613852</v>
+        <v>0.4913485395354307</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5509337854644016</v>
+        <v>0.4913484660384471</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5509337119674179</v>
+        <v>0.4913483925414635</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.121223825302375</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5509337487159099</v>
+        <v>0.4913484292899554</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5509336384704343</v>
+        <v>0.4913483190444798</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5509337487159099</v>
+        <v>0.4913484292899554</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.121223825302375</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5509340427038444</v>
+        <v>0.4913487232778899</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_3_000008.xlsx
+++ b/out/MLP-S4_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.121223825302375</v>
+        <v>0.4967284286797661</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.086681742285026</v>
+        <v>0.8633462078326117</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-0.4031249087787711</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.121223825302375</v>
+        <v>0.1301106495269204</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.686681742285026</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-0.4031249087787711</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.4031249087787711</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.121223825302375</v>
+        <v>0.1301106495269204</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.686681742285026</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-0.4031249087787711</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.4031249087787711</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.121223825302375</v>
+        <v>0.1301106495269204</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5212238253023744</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.686681742285026</v>
+        <v>0.1301106495269204</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.121223825302375</v>
+        <v>0.1301106495269204</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.121223825302375</v>
+        <v>0.1301106495269204</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.086681742285026</v>
+        <v>0.8633462078326117</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.086681742285026</v>
+        <v>1.596581766138303</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000161282156629255</v>
+        <v>-0.0001409794442369603</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1852822208733912</v>
+        <v>-0.1619583038300854</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.121223825302375</v>
+        <v>0.1301106495269204</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.121223825302375</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1854435030300203</v>
+        <v>-0.1620992832743225</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1855801622144</v>
+        <v>-0.1622055482048991</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4913953041836275</v>
+        <v>0.3821044895132683</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7981539431311669</v>
+        <v>0.6027370854336903</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03501181225172942</v>
+        <v>0.02722486465272006</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3759940114468096</v>
+        <v>0.2744693876843266</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06139866110619391</v>
+        <v>0.04774313651467544</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.686681742285026</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4637680940921143</v>
+        <v>0.3427217104914298</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07459243390622572</v>
+        <v>0.05800227244565328</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5515482020194041</v>
+        <v>0.4109785760832971</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01973886192667928</v>
+        <v>0.01534885454750042</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.1301106495269204</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5163385875598644</v>
+        <v>0.3835999591882392</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01096632422859805</v>
+        <v>0.008526254760468787</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.086681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5185132393532288</v>
+        <v>0.3852898185178987</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02304118677646382</v>
+        <v>0.01791612911455526</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5536434304907254</v>
+        <v>0.4126059913498168</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009048986415375181</v>
+        <v>0.007034970978140173</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5486807682013823</v>
+        <v>0.4087460634602194</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006442807535277953</v>
+        <v>0.005009386437948906</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5525141388292953</v>
+        <v>0.4117257204493107</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002532898650642417</v>
+        <v>0.001968015911922649</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5511317429156438</v>
+        <v>0.4106498220350456</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001436221311153854</v>
+        <v>0.001115607372415884</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5514684493514547</v>
+        <v>0.4109105124936921</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000543430430728364</v>
+        <v>0.0004212960307374651</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5511191119218359</v>
+        <v>0.410637776507861</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002526247437593843</v>
+        <v>0.0001953748007017433</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5510793656646519</v>
+        <v>0.4106057516411622</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.9457059439415e-05</v>
+        <v>6.846660178621169e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5510054389294463</v>
+        <v>0.4105471419582248</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.266517359622213e-05</v>
+        <v>1.64643588246551e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5509616995783185</v>
+        <v>0.4105120114345301</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>5.970672288157051e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5509566779836994</v>
+        <v>0.4105069943077632</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5509527686073505</v>
+        <v>0.4105028308469325</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5509505176796189</v>
+        <v>0.4105000297010548</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5509449260196106</v>
+        <v>0.4104945859560484</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5509386020256027</v>
+        <v>0.4104885932226181</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5509332342370243</v>
+        <v>0.4104832254340397</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.550933270985516</v>
+        <v>0.4104832621825314</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5509333812309916</v>
+        <v>0.410483372428007</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5509334547279752</v>
+        <v>0.4104834459249906</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.121223825302375</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5509336384704343</v>
+        <v>0.4104836296674497</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.686681742285026</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5509351819070908</v>
+        <v>0.4104851731041062</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5509366518467639</v>
+        <v>0.4104866430437793</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5509379012954859</v>
+        <v>0.4104878924925013</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5509392609896833</v>
+        <v>0.4104892521866986</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.686681742285026</v>
+        <v>1.796581766138304</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.550937056080174</v>
+        <v>0.4104870472771893</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5509366518467639</v>
+        <v>0.4104866430437793</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5509358066314519</v>
+        <v>0.4104857978284673</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5509363578588292</v>
+        <v>0.4104863490558446</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5509360271224027</v>
+        <v>0.4104860183194182</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5509357331344683</v>
+        <v>0.4104857243314837</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5509358066314519</v>
+        <v>0.4104857978284673</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.55093536564955</v>
+        <v>0.4104853568465654</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5509352554040744</v>
+        <v>0.4104852466010898</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5509352186555827</v>
+        <v>0.4104852098525981</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.121223825302375</v>
+        <v>0.1301106495269204</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.55093536564955</v>
+        <v>0.4104853568465654</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5509348879191563</v>
+        <v>0.4104848791161718</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.686681742285026</v>
+        <v>1.063346207832612</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5509358433799436</v>
+        <v>0.410485834576959</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5212238253023744</v>
+        <v>0.3301106495269204</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5509358066314519</v>
+        <v>0.4104857978284673</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5212238253023744</v>
+        <v>-0.4031249087787711</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5509354758950256</v>
+        <v>0.4104854670920409</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5509359168769274</v>
+        <v>0.4104859080739429</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5509352921525664</v>
+        <v>0.4104852833495818</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5509351084101072</v>
+        <v>0.4104850996071226</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5509347041766972</v>
+        <v>0.4104846953737126</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5509338589613852</v>
+        <v>0.4104838501584006</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5509338222128936</v>
+        <v>0.4104838134099089</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5509339692068608</v>
+        <v>0.4104839604038761</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5509338957098772</v>
+        <v>0.4104838869068925</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5509339692068608</v>
+        <v>0.4104839604038761</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5509340059553527</v>
+        <v>0.4104839971523681</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5509338957098772</v>
+        <v>0.4104838869068925</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.550934336691779</v>
+        <v>0.4104843278887945</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5509342264463035</v>
+        <v>0.4104842176433189</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5509341896978116</v>
+        <v>0.410484180894827</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.550934116200828</v>
+        <v>0.4104841073978434</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5509340794523363</v>
+        <v>0.4104840706493517</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5509338589613852</v>
+        <v>0.4104838501584006</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5509337854644016</v>
+        <v>0.410483776661417</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5509337119674179</v>
+        <v>0.4104837031644334</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5509337487159099</v>
+        <v>0.4104837399129253</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5509336384704343</v>
+        <v>0.4104836296674497</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5509337487159099</v>
+        <v>0.4104837399129253</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.121223825302375</v>
+        <v>-0.6031249087787711</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5509340427038444</v>
+        <v>0.4104840339008597</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_3_000008.xlsx
+++ b/out/MLP-S4_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4504552781581879</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4967284286797661</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5174589157104492</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8633462078326117</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.6311854720115662</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.796581766138304</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.665398895740509</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.796581766138304</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.5368091464042664</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.063346207832612</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4620209634304047</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4688203930854797</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4031249087787711</v>
+        <v>0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4240899085998535</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4450669586658478</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4319500327110291</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4586894512176514</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4514214694499969</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4707142412662506</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4671474695205688</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1301106495269204</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5375458598136902</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.480096161365509</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4348466694355011</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4031249087787711</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4383045732975006</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4533334970474243</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4489985704421997</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4459129869937897</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4711313247680664</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4659859240055084</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1301106495269204</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5023053288459778</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4924563467502594</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4879670143127441</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4031249087787711</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4761030375957489</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4031249087787711</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4851769804954529</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4935601651668549</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1301106495269204</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5205652713775635</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.063346207832612</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.6745117902755737</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.796581766138304</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.5431955456733704</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.796581766138304</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5228009819984436</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.796581766138304</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5226624011993408</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.063346207832612</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4940549731254578</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.063346207832612</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.5349018573760986</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.1301106495269204</v>
+        <v>-0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4972465038299561</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.1301106495269204</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4947859048843384</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1301106495269204</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5686694979667664</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8633462078326117</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5814117193222046</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.596581766138303</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5665040016174316</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.796581766138304</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6331166625022888</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.796581766138304</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.715422511100769</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.796581766138304</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7004042863845825</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.796581766138304</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001409794442369603</v>
+        <v>-0.0001196160965063609</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1619583038300854</v>
+        <v>-0.1374159204966616</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5229436755180359</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.796581766138304</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5828580260276794</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.063346207832612</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4515772461891174</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1301106495269204</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4789265990257263</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.43707475066185</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4378198087215424</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4221343398094177</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4993812441825867</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4630691111087799</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4858392775058746</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4838658571243286</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4686155915260315</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3301106495269204</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.5026427507400513</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.063346207832612</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1620992832743225</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5874120593070984</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.063346207832612</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1622055482048991</v>
+        <v>-0.1376191723436012</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3821044895132683</v>
+        <v>0.3007348545556521</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4559822976589203</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6027370854336903</v>
+        <v>0.4644284731798686</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02722486465272006</v>
+        <v>0.02142733183229223</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.4875721037387848</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2744693876843266</v>
+        <v>0.2060653562563302</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04774313651467544</v>
+        <v>0.03757611096979401</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5466096997261047</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3301106495269204</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3427217104914298</v>
+        <v>0.2597833525048359</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05800227244565328</v>
+        <v>0.04565053712481063</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.44342440366745</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4109785760832971</v>
+        <v>0.3135051078826909</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01534885454750042</v>
+        <v>0.01208027590643986</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3662866652011871</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1301106495269204</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3835999591882392</v>
+        <v>0.2919565449340034</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008526254760468787</v>
+        <v>0.006709501790061913</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6206791996955872</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.063346207832612</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3852898185178987</v>
+        <v>0.2932855162938063</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01791612911455526</v>
+        <v>0.01410047189130365</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.6125177145004272</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.796581766138304</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4126059913498168</v>
+        <v>0.3147854440076307</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007034970978140173</v>
+        <v>0.005536872904863139</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5552524924278259</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.063346207832612</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4087460634602194</v>
+        <v>0.3117461008848182</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005009386437948906</v>
+        <v>0.003941651589276608</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4425760805606842</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4117257204493107</v>
+        <v>0.3140902220375668</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001968015911922649</v>
+        <v>0.00154842753147936</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4797783493995667</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4106498220350456</v>
+        <v>0.3132423539142546</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001115607372415884</v>
+        <v>0.0008766883315294164</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3873366117477417</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4109105124936921</v>
+        <v>0.3134463978514564</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004212960307374651</v>
+        <v>0.0003308695999749724</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3617170453071594</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.410637776507861</v>
+        <v>0.3132307438810405</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001953748007017433</v>
+        <v>0.0001524373434085126</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3133437931537628</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4106057516411622</v>
+        <v>0.3132045100572058</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.846660178621169e-05</v>
+        <v>5.232009589913218e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3264256715774536</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4105471419582248</v>
+        <v>0.3131573887342317</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.64643588246551e-05</v>
+        <v>1.217148705972408e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3296171128749847</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4105120114345301</v>
+        <v>0.3131285489044171</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.970672288157051e-06</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.317353755235672</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4105069943077632</v>
+        <v>0.3131235355008605</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3571473956108093</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4105028308469325</v>
+        <v>0.3131191898750512</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2907325029373169</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4105000297010548</v>
+        <v>0.3131158395202583</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3047977685928345</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4104945859560484</v>
+        <v>0.3131104701932706</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3070391118526459</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4104885932226181</v>
+        <v>0.3131044774598403</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3339225649833679</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4104832254340397</v>
+        <v>0.3130991096712619</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3413620591163635</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4104832621825314</v>
+        <v>0.3130991464197536</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3405424356460571</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.410483372428007</v>
+        <v>0.3130992566652291</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.3338159918785095</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4104834459249906</v>
+        <v>0.3130993301622127</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.444333553314209</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4104836296674497</v>
+        <v>0.3130995139046719</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.6075595617294312</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4104851731041062</v>
+        <v>0.3131010573413284</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4438778758049011</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4104866430437793</v>
+        <v>0.3131025272810015</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4896202087402344</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4104878924925013</v>
+        <v>0.3131037767297234</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.9750310182571411</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.063346207832612</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4104892521866986</v>
+        <v>0.3131051364239207</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.6068025827407837</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.796581766138304</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4104870472771893</v>
+        <v>0.3131029315144115</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.5750852227210999</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.063346207832612</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4104866430437793</v>
+        <v>0.3131025272810015</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4798788726329803</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.3301106495269204</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4104857978284673</v>
+        <v>0.3131016820656894</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3141006231307983</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4104863490558446</v>
+        <v>0.3131022332930667</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.252886176109314</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4104860183194182</v>
+        <v>0.3131019025566403</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.2844433486461639</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4104857243314837</v>
+        <v>0.3131016085687058</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2956950664520264</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4104857978284673</v>
+        <v>0.3131016820656894</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.2308872938156128</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4104853568465654</v>
+        <v>0.3131012410837875</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3026511371135712</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4104852466010898</v>
+        <v>0.313101130838312</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3354143500328064</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4104852098525981</v>
+        <v>0.3131010940898203</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.2697302401065826</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.1301106495269204</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4104853568465654</v>
+        <v>0.3131012410837875</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5593852400779724</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.063346207832612</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4104848791161718</v>
+        <v>0.3131007633533939</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.5455768704414368</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.063346207832612</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.410485834576959</v>
+        <v>0.3131017188141811</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.289530336856842</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3301106495269204</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4104857978284673</v>
+        <v>0.3131016820656894</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.2736310362815857</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4031249087787711</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4104854670920409</v>
+        <v>0.3131013513292631</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.165446862578392</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4104859080739429</v>
+        <v>0.313101792311165</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.1732020080089569</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4104852833495818</v>
+        <v>0.3131011675868039</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.2230334430932999</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4104850996071226</v>
+        <v>0.3131009838443448</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.2251662909984589</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4104846953737126</v>
+        <v>0.3131005796109347</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.1965792328119278</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4104838501584006</v>
+        <v>0.3130997343956227</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3021153509616852</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4104838134099089</v>
+        <v>0.313099697647131</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3209255933761597</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4104839604038761</v>
+        <v>0.3130998446410983</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3577196896076202</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4104838869068925</v>
+        <v>0.3130997711441147</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.4957729279994965</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4104839604038761</v>
+        <v>0.3130998446410983</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2987335026264191</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4104839971523681</v>
+        <v>0.3130998813895902</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.4642238318920135</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4104838869068925</v>
+        <v>0.3130997711441147</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.282514899969101</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4104843278887945</v>
+        <v>0.3131002121260166</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3961010873317719</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4104842176433189</v>
+        <v>0.313100101880541</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2569072544574738</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.410484180894827</v>
+        <v>0.3131000651320491</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.2743041813373566</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4104841073978434</v>
+        <v>0.3130999916350655</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3145072460174561</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4104840706493517</v>
+        <v>0.3130999548865738</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2186554372310638</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4104838501584006</v>
+        <v>0.3130997343956227</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3711473047733307</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6031249087787711</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.410483776661417</v>
+        <v>0.3130996608986391</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3363527357578278</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4104837031644334</v>
+        <v>0.3130995874016555</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3396793901920319</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4104837399129253</v>
+        <v>0.3130996241501474</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3852757811546326</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4104836296674497</v>
+        <v>0.3130995139046719</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4112610220909119</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4104837399129253</v>
+        <v>0.3130996241501474</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4790440797805786</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6031249087787711</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4104840339008597</v>
+        <v>0.3130999181380819</v>
       </c>
     </row>
   </sheetData>
